--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/11_Segundo_Turno_Lula_vs_Flavio_por_Religiao.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/11_Segundo_Turno_Lula_vs_Flavio_por_Religiao.xlsx
@@ -23,7 +23,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linhas_publicadas" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados_Catolicos'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo_Catolicos'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto_Catolicos'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Suavizados_Evangelicos'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IC_Baixo_Evangelicos'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IC_Alto_Evangelicos'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Suavizados_Outras_Religioes'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'IC_Baixo_Outras_Religioes'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'IC_Alto_Outras_Religioes'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Suavizados_Sem_Religiao'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'IC_Baixo_Sem_Religiao'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'IC_Alto_Sem_Religiao'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cobertura'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Metodologia'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Linhas_publicadas'!$A$1:$X$29</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +50,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,16 +61,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -68,17 +93,35 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,78 +487,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>56.84210526315789</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>43.15789473684211</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>54.46748956548633</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>45.53251043451367</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>54.30709053889007</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>45.69290946110993</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>58.66153002705961</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>41.33846997294037</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>58.14814313357141</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>41.85185686642861</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>58.86648962535021</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>41.13351037464977</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>56.53207066984862</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>43.46792933015136</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -526,78 +601,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>61.95652173913043</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>38.04347826086957</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>64.31753382147987</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>35.68246617852013</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>65.02357521663728</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>34.97642478336272</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>58.84497477756658</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>41.15502522243342</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>62.3516214421723</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>37.64837855782771</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>62.34467735700961</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>37.65532264299038</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>64.81416566861083</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>35.18583433138916</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -608,78 +715,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>56.46274398650038</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>32.54970050823952</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>60.29941866205913</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>31.66435101909938</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>61.0073571582155</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>30.96020672494094</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>54.76393494195115</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>37.07398538681799</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>59.11033283659015</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>34.40708995224556</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>59.17297509429392</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>34.48362038027469</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>61.58078759179848</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>31.95245625457682</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -690,78 +829,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>67.45029949176049</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>43.53725601349962</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>68.33564898090061</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>39.70058133794087</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>69.03979327505907</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>38.9926428417845</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>62.92601461318201</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>45.23606505804884</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>65.59291004775446</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>40.88966716340987</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>65.5163796197253</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>40.82702490570607</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>68.04754374542317</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>38.4192124082015</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -772,33 +943,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>observacoes_publicadas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>primeira_data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>ultima_data</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>numero_institutos</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>institutos</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>amostras_segmento_publicadas</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>fallbacks_amostra_segmento</t>
         </is>
       </c>
     </row>
@@ -811,16 +1007,25 @@
       <c r="B2" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="7" t="n">
         <v>46110</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -832,16 +1037,25 @@
       <c r="B3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="7" t="n">
         <v>46110</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -853,16 +1067,25 @@
       <c r="B4" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="7" t="n">
         <v>46110</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -874,19 +1097,29 @@
       <c r="B5" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="7" t="n">
         <v>46110</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -897,16 +1130,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -918,9 +1155,9 @@
           <t>Universo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Brasil, 2º turno, estimulada, Lula × Flávio.</t>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Brasil, 2º turno, estimulada, Lula × Flávio Bolsonaro.</t>
         </is>
       </c>
     </row>
@@ -930,9 +1167,9 @@
           <t>Abertura</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Grupos publicados de religião; rótulos equivalentes são harmonizados conforme a aba Metodologia.</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Grupos publicados de religião; somente rótulos equivalentes são harmonizados.</t>
         </is>
       </c>
     </row>
@@ -942,7 +1179,7 @@
           <t>Medida</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Lula e adversário convertidos para votos válidos dentro de cada grupo.</t>
         </is>
@@ -951,28 +1188,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amostra e IC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Usa amostra do segmento quando publicada; na ausência, o código aplica fallback conservador e isso não equivale à margem de erro total da pesquisa.</t>
+          <t>Cobertura mínima</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Exige ao menos dois grupos e duas datas publicadas em cada grupo desenhado.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Amostra e faixa</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Usa amostra do segmento quando publicada; na ausência, aplica fallback conservador. A faixa é apenas amostral e aproximada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Interpretação</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral.</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral nem probabilidade de vitória.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -983,128 +1233,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>instituto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>tipo_pesquisa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>frequencia_original</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>amostra_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>margem_erro_pp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>nivel_confianca_pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>turno</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>tipo_cenario</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>cenario</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>adversario</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>nivel_geografico</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>geografia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>segmento_tipo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>amostra_segmento</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>lula_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>adversario_pct</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>outros_candidatos_pct</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>brancos_nulos_indecisos_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>base_voto</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>_linha_excel</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>peso_legacy</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>grupo_abertura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="7" t="n">
         <v>46110</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1189,16 +1470,19 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>560</v>
+      </c>
+      <c r="W2" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="7" t="n">
         <v>46110</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1283,16 +1567,19 @@
         </is>
       </c>
       <c r="V3" t="n">
+        <v>561</v>
+      </c>
+      <c r="W3" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="7" t="n">
         <v>46110</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1377,16 +1664,19 @@
         </is>
       </c>
       <c r="V4" t="n">
+        <v>562</v>
+      </c>
+      <c r="W4" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="7" t="n">
         <v>46110</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1471,16 +1761,19 @@
         </is>
       </c>
       <c r="V5" t="n">
+        <v>563</v>
+      </c>
+      <c r="W5" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1565,16 +1858,19 @@
         </is>
       </c>
       <c r="V6" t="n">
+        <v>832</v>
+      </c>
+      <c r="W6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1659,16 +1955,19 @@
         </is>
       </c>
       <c r="V7" t="n">
+        <v>833</v>
+      </c>
+      <c r="W7" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1753,16 +2052,19 @@
         </is>
       </c>
       <c r="V8" t="n">
+        <v>834</v>
+      </c>
+      <c r="W8" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1847,16 +2149,19 @@
         </is>
       </c>
       <c r="V9" t="n">
+        <v>835</v>
+      </c>
+      <c r="W9" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="7" t="n">
         <v>46166</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1941,16 +2246,19 @@
         </is>
       </c>
       <c r="V10" t="n">
+        <v>1080</v>
+      </c>
+      <c r="W10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="7" t="n">
         <v>46166</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2035,16 +2343,19 @@
         </is>
       </c>
       <c r="V11" t="n">
+        <v>1081</v>
+      </c>
+      <c r="W11" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="7" t="n">
         <v>46166</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2129,16 +2440,19 @@
         </is>
       </c>
       <c r="V12" t="n">
+        <v>1082</v>
+      </c>
+      <c r="W12" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="7" t="n">
         <v>46166</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2223,16 +2537,19 @@
         </is>
       </c>
       <c r="V13" t="n">
+        <v>1083</v>
+      </c>
+      <c r="W13" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2253,7 +2570,7 @@
       <c r="E14" t="n">
         <v>2000</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G14" t="n">
@@ -2299,16 +2616,16 @@
           <t>Católica</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="6" t="n">
         <v>55.5</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="6" t="n">
         <v>35.7</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="U14" t="inlineStr">
@@ -2317,16 +2634,19 @@
         </is>
       </c>
       <c r="V14" t="n">
+        <v>1272</v>
+      </c>
+      <c r="W14" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2347,7 +2667,7 @@
       <c r="E15" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G15" t="n">
@@ -2393,16 +2713,16 @@
           <t>Evangélica</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="6" t="n">
         <v>31.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="6" t="n">
         <v>59.2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="U15" t="inlineStr">
@@ -2411,16 +2731,19 @@
         </is>
       </c>
       <c r="V15" t="n">
+        <v>1273</v>
+      </c>
+      <c r="W15" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2441,7 +2764,7 @@
       <c r="E16" t="n">
         <v>2000</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G16" t="n">
@@ -2487,7 +2810,7 @@
           <t>Outras Religiões</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="6" t="n">
         <v>40.8</v>
       </c>
       <c r="R16" t="n">
@@ -2496,7 +2819,7 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" s="6" t="n">
         <v>7.2</v>
       </c>
       <c r="U16" t="inlineStr">
@@ -2505,16 +2828,19 @@
         </is>
       </c>
       <c r="V16" t="n">
+        <v>1276</v>
+      </c>
+      <c r="W16" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2535,7 +2861,7 @@
       <c r="E17" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
@@ -2581,16 +2907,16 @@
           <t>Nenhuma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="6" t="n">
         <v>49.4</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" s="6" t="n">
         <v>39.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" s="6" t="n">
         <v>10.9</v>
       </c>
       <c r="U17" t="inlineStr">
@@ -2599,16 +2925,19 @@
         </is>
       </c>
       <c r="V17" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W17" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2693,16 +3022,19 @@
         </is>
       </c>
       <c r="V18" t="n">
+        <v>1477</v>
+      </c>
+      <c r="W18" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2787,16 +3119,19 @@
         </is>
       </c>
       <c r="V19" t="n">
+        <v>1478</v>
+      </c>
+      <c r="W19" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2881,16 +3216,19 @@
         </is>
       </c>
       <c r="V20" t="n">
+        <v>1479</v>
+      </c>
+      <c r="W20" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2975,16 +3313,19 @@
         </is>
       </c>
       <c r="V21" t="n">
+        <v>1480</v>
+      </c>
+      <c r="W21" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -3069,16 +3410,19 @@
         </is>
       </c>
       <c r="V22" t="n">
+        <v>1712</v>
+      </c>
+      <c r="W22" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -3163,16 +3507,19 @@
         </is>
       </c>
       <c r="V23" t="n">
+        <v>1713</v>
+      </c>
+      <c r="W23" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3257,16 +3604,19 @@
         </is>
       </c>
       <c r="V24" t="n">
+        <v>1714</v>
+      </c>
+      <c r="W24" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3351,16 +3701,19 @@
         </is>
       </c>
       <c r="V25" t="n">
+        <v>1715</v>
+      </c>
+      <c r="W25" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3445,16 +3798,19 @@
         </is>
       </c>
       <c r="V26" t="n">
+        <v>1956</v>
+      </c>
+      <c r="W26" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3539,16 +3895,19 @@
         </is>
       </c>
       <c r="V27" t="n">
+        <v>1957</v>
+      </c>
+      <c r="W27" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -3633,16 +3992,19 @@
         </is>
       </c>
       <c r="V28" t="n">
+        <v>1958</v>
+      </c>
+      <c r="W28" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -3727,15 +4089,19 @@
         </is>
       </c>
       <c r="V29" t="n">
+        <v>1959</v>
+      </c>
+      <c r="W29" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3746,78 +4112,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>51.23740145150886</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>37.55319092519308</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>50.27455247644556</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>41.3395733454729</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>50.11646211967091</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>41.50228104189078</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>54.59575179939296</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>37.27269174527373</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>54.84635594033964</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>38.55006967319684</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>55.63612459513065</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>37.90314534443021</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>53.18444505517436</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>40.1203037154771</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3828,78 +4226,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>62.44680907480692</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>48.76259854849114</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>58.6604266545271</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>49.72544752355444</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>58.49771895810922</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>49.88353788032909</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>62.72730825472626</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>45.40424820060702</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>61.44993032680318</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>45.15364405966037</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>62.09685465556978</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>44.36387540486934</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>59.87969628452289</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>46.81555494482563</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3910,78 +4340,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>31.86813186813187</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>68.13186813186813</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>35.96282870453039</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>64.03717129546962</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>39.34079226822368</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>60.65920773177632</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>36.69712408685394</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>63.30287591314605</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>36.62559869489597</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>63.37440130510404</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>35.30007485126298</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>64.69992514873701</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>37.18686155650887</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>62.81313844349113</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3992,78 +4454,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>26.59533652537532</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>62.85907278911158</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>31.9099402653865</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>59.98428285632573</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>35.22523097784833</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>56.54364644140097</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>32.72028488938332</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>59.32603671567544</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>33.40168677855362</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>60.15048938876169</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>32.16100737926684</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>61.56085767674087</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>33.92218330176934</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>59.5484601887516</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4074,78 +4568,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>37.14092721088841</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>73.40466347462468</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>40.01571714367427</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>68.0900597346135</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>43.45635355859903</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>64.77476902215167</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>40.67396328432456</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>67.27971511061666</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>39.84951061123832</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>66.5983132214464</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>38.43914232325911</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>67.83899262073315</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>40.4515398112484</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>66.07781669823066</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4156,78 +4682,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>55.17241379310344</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>44.82758620689656</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>57.6754790123743</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>42.3245209876257</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>62.80999845730287</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>37.19000154269712</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>51.55216400752859</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>48.4478359924714</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>54.04846817763378</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>45.95153182236623</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>51.79169712808023</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>48.20830287191976</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>55.14080799323447</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>44.85919200676552</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4238,78 +4796,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>49.54484084579973</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>39.20001325959284</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>53.52589511358684</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>38.17493708883825</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>58.76479802499966</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>33.14480111039391</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>47.47542388533026</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>44.37109587027307</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>50.74759061118805</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>42.65065425592051</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>48.53373340081012</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>44.95033914464965</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>51.78110282466584</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>41.49948683819689</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4320,78 +4910,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>60.79998674040716</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>50.45515915420027</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>61.82506291116175</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>46.47410488641316</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>66.85519888960607</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>41.23520197500033</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>55.62890412972692</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>52.52457611466973</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>57.34934574407951</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>49.25240938881196</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>55.04966085535034</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>51.46626659918986</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>58.50051316180311</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>48.21889717533415</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>